--- a/output/full_scan/batch_seq3_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq3_2026-08-10.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:O166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>2603</v>
+        <v>2615</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>914.6973936168118</v>
+        <v>948.4947976488004</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>214</v>
+        <v>87.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.21150049694037</v>
+        <v>61.72244129016575</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13.62504243187257</v>
+        <v>29.26753021560877</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.563752095261533</v>
+        <v>1.704133122305071</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.137254288561303</v>
+        <v>0.132836780581957</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3003</v>
+        <v>2603</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>911.8411619707052</v>
+        <v>914.6973936168118</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>68.7</v>
+        <v>214</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>65.86116568406096</v>
+        <v>64.21150049694037</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.58128381794142</v>
+        <v>13.62504243187257</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.740749205878723</v>
+        <v>1.563752095261533</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.051198209248054</v>
+        <v>1.137254288561303</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3022</v>
+        <v>3003</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>威強電</t>
+          <t>健和興</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>797.8081335414315</v>
+        <v>911.8411619707052</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>113</v>
+        <v>68.7</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>74.56973890538526</v>
+        <v>65.86116568406096</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.76046015094986</v>
+        <v>23.58128381794142</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.380813354143157</v>
+        <v>5.740749205878723</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.061748813315483</v>
+        <v>1.051198209248054</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2465</v>
+        <v>3022</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>麗臺</t>
+          <t>威強電</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>770.6532230878273</v>
+        <v>797.8081335414315</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>93.59999999999999</v>
+        <v>113</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.87149822058865</v>
+        <v>74.56973890538526</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16.64831559516961</v>
+        <v>25.76046015094986</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.603037798463648</v>
+        <v>2.380813354143157</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.618359686159969</v>
+        <v>2.061748813315483</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3046</v>
+        <v>2465</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>麗臺</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>743.8287453736968</v>
+        <v>770.6532230878273</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>59.1</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>64.9996971056014</v>
+        <v>65.87149822058865</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.788829696551</v>
+        <v>16.64831559516961</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.422463967946321</v>
+        <v>3.603037798463648</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5995674501567473</v>
+        <v>1.618359686159969</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3034</v>
+        <v>3046</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>742.6920166013992</v>
+        <v>743.8287453736968</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>544</v>
+        <v>59.1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>60.1966374443771</v>
+        <v>64.9996971056014</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.43220784631002</v>
+        <v>15.788829696551</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6029669031680515</v>
+        <v>2.422463967946321</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>5.500977092129045</v>
+        <v>0.5995674501567473</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>2464</v>
+        <v>3034</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>盟立</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>717.9086884776681</v>
+        <v>742.6920166013992</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>180</v>
+        <v>544</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>62.52078310028837</v>
+        <v>60.1966374443771</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17.23110323381778</v>
+        <v>22.43220784631002</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.837464698529945</v>
+        <v>0.6029669031680515</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5.105568713711019</v>
+        <v>5.500977092129045</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3006</v>
+        <v>2464</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>盟立</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>683.2931130603703</v>
+        <v>717.9086884776681</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>275.5</v>
+        <v>180</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.10323582925756</v>
+        <v>62.52078310028837</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.28127756476113</v>
+        <v>17.23110323381778</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.955692478183364</v>
+        <v>1.837464698529945</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>9.398108120748946</v>
+        <v>5.105568713711019</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>2607</v>
+        <v>3006</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>671.0611044749234</v>
+        <v>683.2931130603703</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>48.5</v>
+        <v>275.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.09966062299221</v>
+        <v>66.10323582925756</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.70452679350598</v>
+        <v>19.28127756476113</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.288224724969028</v>
+        <v>1.955692478183364</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.1695987930092307</v>
+        <v>9.398108120748946</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3088</v>
+        <v>2607</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>艾訊</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>669.9580497439214</v>
+        <v>671.0611044749234</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>146</v>
+        <v>48.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.67236447158457</v>
+        <v>60.09966062299221</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>17.40442559866501</v>
+        <v>21.70452679350598</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.095804974392134</v>
+        <v>1.288224724969028</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8530144819037835</v>
+        <v>0.1695987930092307</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>2605</v>
+        <v>3088</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>艾訊</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>652.5285075185534</v>
+        <v>669.9580497439214</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>33.1</v>
+        <v>146</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.98573547835219</v>
+        <v>57.67236447158457</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13.15602727871204</v>
+        <v>17.40442559866501</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.162619405476087</v>
+        <v>1.095804974392134</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2067025760831067</v>
+        <v>0.8530144819037835</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2478</v>
+        <v>2605</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>643.1459481331219</v>
+        <v>652.5285075185534</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>122</v>
+        <v>33.1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>42.15913882256757</v>
+        <v>61.98573547835219</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.29677228315701</v>
+        <v>13.15602727871204</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.7056639726366593</v>
+        <v>1.162619405476087</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.72016365282383</v>
+        <v>0.2067025760831067</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3036</v>
+        <v>2478</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>603.7819156777188</v>
+        <v>643.1459481331219</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>229</v>
+        <v>122</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.29363305422201</v>
+        <v>42.15913882256757</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.47873345011212</v>
+        <v>27.29677228315701</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.605858933259593</v>
+        <v>0.7056639726366593</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>5.004469653634482</v>
+        <v>0.72016365282383</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2474</v>
+        <v>2637</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>600.5273807815998</v>
+        <v>642.3343294775198</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>201</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.02380562850364</v>
+        <v>65.88779083135736</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17.1998104859835</v>
+        <v>22.30190138522042</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.368421626191824</v>
+        <v>0.8156100707882709</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.775406296250344</v>
+        <v>0.5561156006133237</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3081</v>
+        <v>3036</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>597.0372645183335</v>
+        <v>603.7819156777188</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2535</v>
+        <v>229</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>66.63116287140555</v>
+        <v>58.29363305422201</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.52815742371192</v>
+        <v>24.47873345011212</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.055885789137914</v>
+        <v>1.605858933259593</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>117.7076233079549</v>
+        <v>5.004469653634482</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2466</v>
+        <v>2474</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>冠西電</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>592.1027774378128</v>
+        <v>600.5273807815998</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>201</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.92685704771301</v>
+        <v>61.02380562850364</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.40683554865186</v>
+        <v>17.1998104859835</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.129872125698296</v>
+        <v>2.368421626191824</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-2.41636950391954</v>
+        <v>1.775406296250344</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>2606</v>
+        <v>3081</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>585.0915836465188</v>
+        <v>597.0372645183335</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>66.8</v>
+        <v>2535</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.78181000131734</v>
+        <v>66.63116287140555</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16.06635405110258</v>
+        <v>22.52815742371192</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9359147787019958</v>
+        <v>1.055885789137914</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5692744380789682</v>
+        <v>117.7076233079549</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3010</v>
+        <v>2466</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>華立</t>
+          <t>冠西電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>564.02394207641</v>
+        <v>592.1027774378128</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>122.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.45545558695238</v>
+        <v>54.92685704771301</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.84075658386884</v>
+        <v>33.40683554865186</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6972197160463588</v>
+        <v>1.129872125698296</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.390655922583485</v>
+        <v>-2.41636950391954</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2516</v>
+        <v>2606</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>563.6011744390669</v>
+        <v>585.0915836465188</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.1</v>
+        <v>66.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.0014418803713</v>
+        <v>61.78181000131734</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>53.68000763398474</v>
+        <v>16.06635405110258</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5005529665191717</v>
+        <v>0.9359147787019958</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0182693856501233</v>
+        <v>0.5692744380789682</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2542</v>
+        <v>3010</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>華立</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>557.75444334</v>
+        <v>564.02394207641</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>44.35</v>
+        <v>122.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.4471770957369</v>
+        <v>55.45545558695238</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.2645217578704</v>
+        <v>20.84075658386884</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4114049665828266</v>
+        <v>0.6972197160463588</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0236829510661385</v>
+        <v>1.390655922583485</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2540</v>
+        <v>2516</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>547.7188189562801</v>
+        <v>563.6011744390669</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45.2</v>
+        <v>14.1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>29.91093155316661</v>
+        <v>56.0014418803713</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.6092875572883</v>
+        <v>53.68000763398474</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.907994200390872</v>
+        <v>0.5005529665191717</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.8197188325403446</v>
+        <v>-0.0182693856501233</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2597</v>
+        <v>2542</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>潤弘</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>542.8359495964258</v>
+        <v>557.75444334</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>168</v>
+        <v>44.35</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.92992435765409</v>
+        <v>55.4471770957369</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16.79088188282712</v>
+        <v>15.2645217578704</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7043069255099856</v>
+        <v>0.4114049665828266</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.9823771593115878</v>
+        <v>0.0236829510661385</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3014</v>
+        <v>2540</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聯陽</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>542.1977230671822</v>
+        <v>547.7188189562801</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>136.5</v>
+        <v>45.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>52.83105339842987</v>
+        <v>29.91093155316661</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.87590060029083</v>
+        <v>21.6092875572883</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.541207758178924</v>
+        <v>1.907994200390872</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.743074262657752</v>
+        <v>-0.8197188325403446</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2497</v>
+        <v>2597</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>怡利電</t>
+          <t>潤弘</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>529.9651275573711</v>
+        <v>542.8359495964258</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>48.25</v>
+        <v>168</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>41.05446244712309</v>
+        <v>55.92992435765409</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>27.12171890466484</v>
+        <v>16.79088188282712</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.3348256781647072</v>
+        <v>0.7043069255099856</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.08963675368257459</v>
+        <v>0.9823771593115878</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>2539</v>
+        <v>3014</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>527.7613199772749</v>
+        <v>542.1977230671822</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>42.85</v>
+        <v>136.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.68658664165608</v>
+        <v>52.83105339842987</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.97952055156527</v>
+        <v>27.87590060029083</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8277179546812564</v>
+        <v>1.541207758178924</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1061483214567937</v>
+        <v>1.743074262657752</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>2536</v>
+        <v>2611</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>宏普</t>
+          <t>志信</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>527.1618458220104</v>
+        <v>530.8712130383782</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>20.3</v>
+        <v>14.25</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.66974972055795</v>
+        <v>58.69612893469721</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.62117681114208</v>
+        <v>20.74943590628797</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.884268747749104</v>
+        <v>1.063355759444769</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2244646032732289</v>
+        <v>0.0177466462089881</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3078</v>
+        <v>2497</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>僑威</t>
+          <t>怡利電</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>523.7987979975151</v>
+        <v>529.9651275573711</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>54.7</v>
+        <v>48.25</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.64970410113421</v>
+        <v>41.05446244712309</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.12934016806001</v>
+        <v>27.12171890466484</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.271643216332178</v>
+        <v>0.3348256781647072</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3784378001348307</v>
+        <v>0.08963675368257459</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2484</v>
+        <v>2539</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>希華</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>521.869833859173</v>
+        <v>527.7613199772749</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>74.3</v>
+        <v>42.85</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.75189917641333</v>
+        <v>59.68658664165608</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19.29449558312294</v>
+        <v>28.97952055156527</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.121196114989633</v>
+        <v>0.8277179546812564</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.1990050254257778</v>
+        <v>0.1061483214567937</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3029</v>
+        <v>2536</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>宏普</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>520.5545121573163</v>
+        <v>527.1618458220104</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>109</v>
+        <v>20.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.59428665609416</v>
+        <v>62.66974972055795</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.58821998674628</v>
+        <v>26.62117681114208</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8049627355906283</v>
+        <v>1.884268747749104</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.5960007638153419</v>
+        <v>0.2244646032732289</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>2492</v>
+        <v>2618</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>514.7163997563299</v>
+        <v>523.9228589805552</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>273.5</v>
+        <v>42.65</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>42.04960545893996</v>
+        <v>51.98890726257413</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>35.61328644966174</v>
+        <v>17.36171060781999</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.25983125545251</v>
+        <v>0.8936079720215706</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>5.468232520739399</v>
+        <v>0.062384746126191</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3017</v>
+        <v>3078</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>僑威</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>512.6003743297354</v>
+        <v>523.7987979975151</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2765</v>
+        <v>54.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>60.19213605579014</v>
+        <v>55.64970410113421</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.98380039393833</v>
+        <v>15.12934016806001</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7218905073841746</v>
+        <v>1.271643216332178</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>69.30214125062739</v>
+        <v>0.3784378001348307</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3114</v>
+        <v>2484</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>好德</t>
+          <t>希華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>511.9657270309897</v>
+        <v>521.869833859173</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>37.5</v>
+        <v>74.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.02302703078853</v>
+        <v>53.75189917641333</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>31.74914561637531</v>
+        <v>19.29449558312294</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.712970991751932</v>
+        <v>1.121196114989633</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.054439022855227</v>
+        <v>0.1990050254257778</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>2472</v>
+        <v>3029</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>505.042023433181</v>
+        <v>520.5545121573163</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>240.5</v>
+        <v>109</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>40.7114440961251</v>
+        <v>58.59428665609416</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27.00626229918607</v>
+        <v>16.58821998674628</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5170707325484688</v>
+        <v>0.8049627355906283</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.102050464836168</v>
+        <v>0.5960007638153419</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>2449</v>
+        <v>2630</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>500.6688804304651</v>
+        <v>516.1098594033467</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>248.5</v>
+        <v>48.3</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.22557282897466</v>
+        <v>45.95690785417352</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.184071297436</v>
+        <v>21.89875945826505</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.456458756065668</v>
+        <v>0.1014505122720665</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.7321293842343159</v>
+        <v>-0.6798792743168222</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>2535</v>
+        <v>2492</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>500.1018900577843</v>
+        <v>514.7163997563299</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>90.5</v>
+        <v>273.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.6288233892798</v>
+        <v>42.04960545893996</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.62508368689552</v>
+        <v>35.61328644966174</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.012461085984047</v>
+        <v>2.25983125545251</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.3523931213585738</v>
+        <v>5.468232520739399</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>2481</v>
+        <v>3017</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>500.02260481412</v>
+        <v>512.6003743297354</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>137.5</v>
+        <v>2765</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>46.08240949167038</v>
+        <v>60.19213605579014</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.95456593275888</v>
+        <v>18.98380039393833</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6075581417548003</v>
+        <v>0.7218905073841746</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.752970986133116</v>
+        <v>69.30214125062739</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3090</v>
+        <v>3114</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>好德</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>499.4464689954098</v>
+        <v>511.9657270309897</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>161</v>
+        <v>37.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.03932236674866</v>
+        <v>55.02302703078853</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29.55284444716854</v>
+        <v>31.74914561637531</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.645891199105746</v>
+        <v>1.712970991751932</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>2.983533323509846</v>
+        <v>1.054439022855227</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>2476</v>
+        <v>2472</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>498.558807487505</v>
+        <v>505.042023433181</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>126</v>
+        <v>240.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>55.31202512071299</v>
+        <v>40.7114440961251</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21.99188616305342</v>
+        <v>27.00626229918607</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8568779287618024</v>
+        <v>0.5170707325484688</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.459724648829721</v>
+        <v>1.102050464836168</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3094</v>
+        <v>2449</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯傑</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>487.3493075974725</v>
+        <v>500.6688804304651</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>36.95</v>
+        <v>248.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.03665208480297</v>
+        <v>44.22557282897466</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.47893216919812</v>
+        <v>21.184071297436</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5485653076414247</v>
+        <v>1.456458756065668</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0980555171735899</v>
+        <v>0.7321293842343159</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>2520</v>
+        <v>2535</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>冠德</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>484.4197464346187</v>
+        <v>500.1018900577843</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>34.85</v>
+        <v>90.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.69159043189172</v>
+        <v>55.6288233892798</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14.99673551563348</v>
+        <v>14.62508368689552</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.855925115591928</v>
+        <v>1.012461085984047</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1344787267356744</v>
+        <v>0.3523931213585738</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>2461</v>
+        <v>2481</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>光群雷</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>481.5948438599207</v>
+        <v>500.02260481412</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>17.5</v>
+        <v>137.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.95310697790661</v>
+        <v>46.08240949167038</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.26451936407957</v>
+        <v>29.95456593275888</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.623348991942278</v>
+        <v>0.6075581417548003</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2190423490495105</v>
+        <v>0.752970986133116</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>2493</v>
+        <v>3090</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>揚博</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>477.5362261221269</v>
+        <v>499.4464689954098</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>218</v>
+        <v>161</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.38160618385475</v>
+        <v>42.03932236674866</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.31995849386187</v>
+        <v>29.55284444716854</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.9159898015282982</v>
+        <v>1.645891199105746</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.914014518801876</v>
+        <v>2.983533323509846</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>2527</v>
+        <v>2476</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>宏璟</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>469.256155128703</v>
+        <v>498.558807487505</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>47.6</v>
+        <v>126</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.32388308799671</v>
+        <v>55.31202512071299</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>26.12705430894423</v>
+        <v>21.99188616305342</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5910117175861999</v>
+        <v>0.8568779287618024</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0967148296075979</v>
+        <v>1.459724648829721</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>2610</v>
+        <v>3094</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>聯傑</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>463.6140575564179</v>
+        <v>487.3493075974725</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>20.45</v>
+        <v>36.95</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40.26037480722405</v>
+        <v>52.03665208480297</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.58038775988869</v>
+        <v>18.47893216919812</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.662727564011731</v>
+        <v>0.5485653076414247</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0378754628621776</v>
+        <v>0.0980555171735899</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>2511</v>
+        <v>2520</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>太子</t>
+          <t>冠德</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>459.2963479085236</v>
+        <v>484.4197464346187</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>8.35</v>
+        <v>34.85</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.1653754140253</v>
+        <v>51.69159043189172</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.61101506312989</v>
+        <v>14.99673551563348</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4286403387071448</v>
+        <v>1.855925115591928</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0341950338606536</v>
+        <v>-0.1344787267356744</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3044</v>
+        <v>2461</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>光群雷</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>455.2983856169089</v>
+        <v>481.5948438599207</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>401.5</v>
+        <v>17.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.12415739838879</v>
+        <v>60.95310697790661</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>35.22637799826057</v>
+        <v>21.26451936407957</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6781535826920128</v>
+        <v>0.623348991942278</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>6.399316984687697</v>
+        <v>0.2190423490495105</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3048</v>
+        <v>2493</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>益登</t>
+          <t>揚博</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>454.4185532379782</v>
+        <v>477.5362261221269</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>57.3</v>
+        <v>218</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.46417449259918</v>
+        <v>49.38160618385475</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>26.86708095182801</v>
+        <v>22.31995849386187</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8195693063479771</v>
+        <v>0.9159898015282982</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.61821965801349</v>
+        <v>0.914014518801876</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3105</v>
+        <v>2527</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>宏璟</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>451.2101918017194</v>
+        <v>469.256155128703</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>385.5</v>
+        <v>47.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.22315113069234</v>
+        <v>58.32388308799671</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.3309629842326</v>
+        <v>26.12705430894423</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.245913137494262</v>
+        <v>0.5910117175861999</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>11.89163687470906</v>
+        <v>-0.0967148296075979</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>2488</v>
+        <v>2610</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>漢平</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>450.1148315783449</v>
+        <v>463.6140575564179</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>49.65</v>
+        <v>20.45</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.2116122558532</v>
+        <v>40.26037480722405</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>32.24439726797805</v>
+        <v>19.58038775988869</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5192693536807443</v>
+        <v>2.662727564011731</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1282208161700475</v>
+        <v>-0.0378754628621776</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>2485</v>
+        <v>2511</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>太子</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>448.1278034207728</v>
+        <v>459.2963479085236</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>44</v>
+        <v>8.35</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.41346928431437</v>
+        <v>48.1653754140253</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>35.52179389085086</v>
+        <v>27.61101506312989</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.523584831748945</v>
+        <v>0.4286403387071448</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>1.234078188321904</v>
+        <v>-0.0341950338606536</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3005</v>
+        <v>3044</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>441.6001405880991</v>
+        <v>455.2983856169089</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>114.5</v>
+        <v>401.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>56.82693450596072</v>
+        <v>46.12415739838879</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.69811831061663</v>
+        <v>35.22637799826057</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8154934030739789</v>
+        <v>0.6781535826920128</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0186281883414098</v>
+        <v>6.399316984687697</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>2547</v>
+        <v>2704</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>日勝生</t>
+          <t>國賓</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>436.0813404368519</v>
+        <v>454.7213377949803</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>10.75</v>
+        <v>46.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.52251499941659</v>
+        <v>53.2340127746718</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.24718410934485</v>
+        <v>28.55342144528791</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.671308651748287</v>
+        <v>0.6372278528717656</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.051502468817436</v>
+        <v>-0.1526458872090479</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>2451</v>
+        <v>3048</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>益登</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>435.5658617168895</v>
+        <v>454.4185532379782</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>295.5</v>
+        <v>57.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>59.6842797594037</v>
+        <v>54.46417449259918</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.53761201376812</v>
+        <v>26.86708095182801</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7011636196137353</v>
+        <v>0.8195693063479771</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>5.771097746206327</v>
+        <v>1.61821965801349</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>2645</v>
+        <v>3105</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>426.9851004336029</v>
+        <v>451.2101918017194</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>189.5</v>
+        <v>385.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>46.4146870137977</v>
+        <v>53.22315113069234</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.66443356926168</v>
+        <v>19.3309629842326</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2694769606433529</v>
+        <v>1.245913137494262</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.531885686813387</v>
+        <v>11.89163687470906</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>2609</v>
+        <v>2488</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>漢平</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>425.1221575451578</v>
+        <v>450.1148315783449</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>51.6</v>
+        <v>49.65</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.57663739307412</v>
+        <v>47.2116122558532</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10.50176455363316</v>
+        <v>32.24439726797805</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.369900058272575</v>
+        <v>0.5192693536807443</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1022803515449272</v>
+        <v>0.1282208161700475</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>2462</v>
+        <v>2485</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>良得電</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>422.0371727044545</v>
+        <v>448.1278034207728</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>32.82297347803778</v>
+        <v>49.41346928431437</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>28.39378572199302</v>
+        <v>35.52179389085086</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9537504874575654</v>
+        <v>1.523584831748945</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0202153692761688</v>
+        <v>1.234078188321904</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>2528</v>
+        <v>3005</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>皇普</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>417.833081966478</v>
+        <v>441.6001405880991</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>20.75</v>
+        <v>114.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.9669468430418</v>
+        <v>56.82693450596072</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.55793835019235</v>
+        <v>21.69811831061663</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6781733428238506</v>
+        <v>0.8154934030739789</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0150704968347481</v>
+        <v>-0.0186281883414098</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3059</v>
+        <v>2547</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>華晶科</t>
+          <t>日勝生</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>416.8352554246742</v>
+        <v>436.0813404368519</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>40.8</v>
+        <v>10.75</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.44646746662363</v>
+        <v>56.52251499941659</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>29.61103318270312</v>
+        <v>21.24718410934485</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6132741465382635</v>
+        <v>0.671308651748287</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.3222780077103746</v>
+        <v>0.051502468817436</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>3033</v>
+        <v>2451</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>威健</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>413.0509648632091</v>
+        <v>435.5658617168895</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>49.35</v>
+        <v>295.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.37184042950766</v>
+        <v>59.6842797594037</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.98784706469105</v>
+        <v>15.53761201376812</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6187077341595389</v>
+        <v>0.7011636196137353</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1377135353295941</v>
+        <v>5.771097746206327</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>2458</v>
+        <v>2645</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>407.7932786852181</v>
+        <v>426.9851004336029</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>145.5</v>
+        <v>189.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.52832517415855</v>
+        <v>46.4146870137977</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.60259285821169</v>
+        <v>21.66443356926168</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.032090681831066</v>
+        <v>0.2694769606433529</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.010941692005247</v>
+        <v>-1.531885686813387</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3054</v>
+        <v>2609</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>立萬利</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>394.9173629843771</v>
+        <v>425.1221575451578</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>48.35</v>
+        <v>51.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>32.38477251301764</v>
+        <v>54.57663739307412</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>40.81964518377582</v>
+        <v>10.50176455363316</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.896669808063748</v>
+        <v>1.369900058272575</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2217000199329071</v>
+        <v>0.1022803515449272</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>2480</v>
+        <v>2462</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>良得電</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>393.2414399347659</v>
+        <v>422.0371727044545</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>154.5</v>
+        <v>19.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.17171346072254</v>
+        <v>32.82297347803778</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>13.38634411751821</v>
+        <v>28.39378572199302</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2960881651615917</v>
+        <v>0.9537504874575654</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.5538660544467608</v>
+        <v>0.0202153692761688</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>2545</v>
+        <v>2633</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>皇翔</t>
+          <t>台灣高鐵</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>379.6089136624379</v>
+        <v>420.8485716749806</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>33.15</v>
+        <v>25.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.95189714399119</v>
+        <v>47.63297538448394</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>39.52734142398004</v>
+        <v>10.63022102095272</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.176898690574714</v>
+        <v>0.7776464460322213</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.07354292548937</v>
+        <v>-0.026845080948497</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3051</v>
+        <v>2634</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力特</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>376.2893881113598</v>
+        <v>418.9522543074693</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>23.3</v>
+        <v>61</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.92579552195909</v>
+        <v>51.18629244999814</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>29.97505201961986</v>
+        <v>33.23210006533195</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.540725429167933</v>
+        <v>0.2120897157967761</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.2762190320267572</v>
+        <v>-0.6502391661222597</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3042</v>
+        <v>2528</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>367.9650999420762</v>
+        <v>417.833081966478</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>180.5</v>
+        <v>20.75</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.14349796366476</v>
+        <v>47.9669468430418</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.05756527121735</v>
+        <v>20.55793835019235</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.9965147447445988</v>
+        <v>0.6781733428238506</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>3.548772286988669</v>
+        <v>0.0150704968347481</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>2495</v>
+        <v>3059</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>華晶科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>367.1784003531237</v>
+        <v>416.8352554246742</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>39</v>
+        <v>40.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.99259367768705</v>
+        <v>46.44646746662363</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>29.92683752083955</v>
+        <v>29.61103318270312</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6883105943000232</v>
+        <v>0.6132741465382635</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.5998058717637402</v>
+        <v>0.3222780077103746</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3002</v>
+        <v>3033</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>歐格</t>
+          <t>威健</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>363.4825250208335</v>
+        <v>413.0509648632091</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>16.9</v>
+        <v>49.35</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.2110136952464</v>
+        <v>53.37184042950766</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.70074008316958</v>
+        <v>16.98784706469105</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.95126088326352</v>
+        <v>0.6187077341595389</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0447750971986743</v>
+        <v>0.1377135353295941</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>2486</v>
+        <v>2458</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>一詮</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>361.7307695434379</v>
+        <v>407.7932786852181</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>233</v>
+        <v>145.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.33621402892573</v>
+        <v>38.52832517415855</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10.71232333213177</v>
+        <v>20.60259285821169</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.219273838655369</v>
+        <v>1.032090681831066</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>3.676391019852309</v>
+        <v>-2.010941692005247</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>2546</v>
+        <v>3054</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>根基</t>
+          <t>立萬利</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>361.6985652379636</v>
+        <v>394.9173629843771</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>48.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.37148749242899</v>
+        <v>32.38477251301764</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>42.111817555884</v>
+        <v>40.81964518377582</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.273506834887286</v>
+        <v>1.896669808063748</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.4718017470416074</v>
+        <v>0.2217000199329071</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>2483</v>
+        <v>2480</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>百容</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>354.4362311330428</v>
+        <v>393.2414399347659</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>35.85</v>
+        <v>154.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.93015844193275</v>
+        <v>47.17171346072254</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>27.53210099805772</v>
+        <v>13.38634411751821</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6725586930232381</v>
+        <v>0.2960881651615917</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5412585086616009</v>
+        <v>-0.5538660544467608</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>2459</v>
+        <v>2612</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>中航</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>352.7045574379148</v>
+        <v>389.5232214448727</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>55</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>58.24922315713017</v>
+        <v>58.81604502393591</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.83078800923142</v>
+        <v>20.24385817526141</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.148019940892266</v>
+        <v>0.871865099164324</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1473692963923848</v>
+        <v>0.4762150123725617</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3032</v>
+        <v>2545</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>偉訓</t>
+          <t>皇翔</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>350.8176964368612</v>
+        <v>379.6089136624379</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>81.3</v>
+        <v>33.15</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>52.04891576686103</v>
+        <v>40.95189714399119</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.72519796789763</v>
+        <v>39.52734142398004</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6334141480822716</v>
+        <v>1.176898690574714</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.6997950537507275</v>
+        <v>0.07354292548937</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3028</v>
+        <v>3051</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>增你強</t>
+          <t>力特</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>349.3506949399817</v>
+        <v>376.2893881113598</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>68.5</v>
+        <v>23.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.26880076473024</v>
+        <v>48.92579552195909</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.0962605933798</v>
+        <v>29.97505201961986</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.918421689181138</v>
+        <v>1.540725429167933</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.967454189140581</v>
+        <v>0.2762190320267572</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>2467</v>
+        <v>3042</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>344.2090560691541</v>
+        <v>367.9650999420762</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>550</v>
+        <v>180.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.47579597651894</v>
+        <v>53.14349796366476</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.77961741558531</v>
+        <v>16.05756527121735</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8911548030851815</v>
+        <v>0.9965147447445988</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>4.802034223312038</v>
+        <v>3.548772286988669</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3008</v>
+        <v>2495</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>340.9293849011565</v>
+        <v>367.1784003531237</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>4400</v>
+        <v>39</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>55.24785885679813</v>
+        <v>46.99259367768705</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.84350681886587</v>
+        <v>29.92683752083955</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7702265449277572</v>
+        <v>0.6883105943000232</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>58.16402779660028</v>
+        <v>0.5998058717637402</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3115</v>
+        <v>2613</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>富榮綱</t>
+          <t>中櫃</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>340.6743576034537</v>
+        <v>366.8485306748423</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>9</v>
+        <v>20.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.05641613802274</v>
+        <v>41.75704827848007</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12.53844315383208</v>
+        <v>34.72722140012997</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.848031295178162</v>
+        <v>0.5283147016926318</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5365991247433606</v>
+        <v>0.0134476671391627</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3016</v>
+        <v>3002</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>嘉晶</t>
+          <t>歐格</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>339.851386009154</v>
+        <v>363.4825250208335</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>107</v>
+        <v>16.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.47940479596441</v>
+        <v>41.2110136952464</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.57346749745182</v>
+        <v>24.70074008316958</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7777205531031339</v>
+        <v>0.95126088326352</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>2.193358086574362</v>
+        <v>0.0447750971986743</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>2491</v>
+        <v>2486</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>吉祥全</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>317.7479380815101</v>
+        <v>361.7307695434379</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>34.9</v>
+        <v>233</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>60.52121122346423</v>
+        <v>52.33621402892573</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>28.87258559909288</v>
+        <v>10.71232333213177</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6951244059536423</v>
+        <v>1.219273838655369</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.846333751486672</v>
+        <v>3.676391019852309</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3031</v>
+        <v>2546</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>佰鴻</t>
+          <t>根基</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>316.6971128753713</v>
+        <v>361.6985652379636</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>23.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.14157301879787</v>
+        <v>40.37148749242899</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>29.54678518212281</v>
+        <v>42.111817555884</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6099633038872714</v>
+        <v>1.273506834887286</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2556375946608837</v>
+        <v>-0.4718017470416074</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3035</v>
+        <v>2483</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>百容</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>314.8311053406738</v>
+        <v>354.4362311330428</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>178</v>
+        <v>35.85</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>46.49749460684604</v>
+        <v>40.93015844193275</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>30.61832760156753</v>
+        <v>27.53210099805772</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.992331312800382</v>
+        <v>0.6725586930232381</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.008392715652638201</v>
+        <v>-0.5412585086616009</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>2498</v>
+        <v>2459</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>314.6675695765028</v>
+        <v>352.7045574379148</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>40.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.0055206922787</v>
+        <v>58.24922315713017</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.09116210158142</v>
+        <v>13.83078800923142</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.8372916750221183</v>
+        <v>1.148019940892266</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1074172968228002</v>
+        <v>0.1473692963923848</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>2454</v>
+        <v>3032</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>偉訓</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>311.8608158901647</v>
+        <v>350.8176964368612</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>3960</v>
+        <v>81.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>54.39593636666147</v>
+        <v>52.04891576686103</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14.53349442437364</v>
+        <v>14.72519796789763</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5935465261752649</v>
+        <v>0.6334141480822716</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>62.121408043058</v>
+        <v>0.6997950537507275</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>2504</v>
+        <v>3028</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>增你強</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>310.6127975392235</v>
+        <v>349.3506949399817</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>30.95</v>
+        <v>68.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.16377460421602</v>
+        <v>49.26880076473024</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>25.09243858182507</v>
+        <v>19.0962605933798</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4802914770499117</v>
+        <v>0.918421689181138</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0326716940120571</v>
+        <v>0.967454189140581</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3066</v>
+        <v>2712</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>李洲</t>
+          <t>遠雄來</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>305.340194608515</v>
+        <v>349.3475203014727</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>22.55</v>
+        <v>14.95</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>50.29544575487587</v>
+        <v>51.85958632230606</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.3891757059414</v>
+        <v>13.3026107163885</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.447992840226985</v>
+        <v>0.3063817067702884</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1527763254325799</v>
+        <v>-0.3891396734560348</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>3073</v>
+        <v>2467</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>天方能源</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>305.0462918429703</v>
+        <v>344.2090560691541</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>22.1</v>
+        <v>550</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.73079482690229</v>
+        <v>52.47579597651894</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.68169556160542</v>
+        <v>17.77961741558531</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4078559020457727</v>
+        <v>0.8911548030851815</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0520028234179424</v>
+        <v>4.802034223312038</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>3085</v>
+        <v>3008</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>新零售</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>304.5047696586732</v>
+        <v>340.9293849011565</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>11.75</v>
+        <v>4400</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>53.44326793618968</v>
+        <v>55.24785885679813</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.05060828317397</v>
+        <v>17.84350681886587</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.45034532031436</v>
+        <v>0.7702265449277572</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.951588987715273</v>
+        <v>58.16402779660028</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>2496</v>
+        <v>3115</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>卓越</t>
+          <t>富榮綱</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>303.9891389872214</v>
+        <v>340.6743576034537</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>59.4</v>
+        <v>9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>39.27390875432424</v>
+        <v>54.05641613802274</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>38.99775260467082</v>
+        <v>12.53844315383208</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8911398655471982</v>
+        <v>2.848031295178162</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1567590934338771</v>
+        <v>0.5365991247433606</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>2501</v>
+        <v>3016</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>國建</t>
+          <t>嘉晶</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>303.4380578348697</v>
+        <v>339.851386009154</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>22.2</v>
+        <v>107</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.77794615163543</v>
+        <v>52.47940479596441</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>25.04474904649135</v>
+        <v>16.57346749745182</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6415007638695015</v>
+        <v>0.7777205531031339</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0310344934648875</v>
+        <v>2.193358086574362</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>3060</v>
+        <v>2491</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>銘異</t>
+          <t>吉祥全</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>299.2994207396545</v>
+        <v>317.7479380815101</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>29.55</v>
+        <v>34.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.40820166474667</v>
+        <v>60.52121122346423</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>23.02496503499644</v>
+        <v>28.87258559909288</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9737597969185304</v>
+        <v>0.6951244059536423</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2620894114027035</v>
+        <v>0.846333751486672</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>2543</v>
+        <v>3031</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>皇昌</t>
+          <t>佰鴻</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>297.7816852075697</v>
+        <v>316.6971128753713</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>38.9</v>
+        <v>23.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>50.14558381475259</v>
+        <v>42.14157301879787</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.39351662212618</v>
+        <v>29.54678518212281</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7857299181036159</v>
+        <v>0.6099633038872714</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.308277961194473</v>
+        <v>0.2556375946608837</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>3093</v>
+        <v>3035</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>297.717852375314</v>
+        <v>314.8311053406738</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>48</v>
+        <v>178</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.7160175716494</v>
+        <v>46.49749460684604</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>32.43471002480614</v>
+        <v>30.61832760156753</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2994109505423246</v>
+        <v>0.992331312800382</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.8072366987866797</v>
+        <v>-0.008392715652638201</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>2601</v>
+        <v>2498</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>益航</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>297.5212102614102</v>
+        <v>314.6675695765028</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>6.32</v>
+        <v>40.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.2704801971728</v>
+        <v>46.0055206922787</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.83757078601122</v>
+        <v>21.09116210158142</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4196565368759983</v>
+        <v>0.8372916750221183</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0553170553549568</v>
+        <v>0.1074172968228002</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>2489</v>
+        <v>2454</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>瑞軒</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>296.6200899080137</v>
+        <v>311.8608158901647</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>33.4</v>
+        <v>3960</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.30184868441617</v>
+        <v>54.39593636666147</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>35.58132726560577</v>
+        <v>14.53349442437364</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.302878452483696</v>
+        <v>0.5935465261752649</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.9257096644621096</v>
+        <v>62.121408043058</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>2949</v>
+        <v>2707</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>欣新網</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>296.0386053580718</v>
+        <v>310.8742956427795</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>62.8</v>
+        <v>180</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.57058808969348</v>
+        <v>54.44541559453504</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14.89546132722419</v>
+        <v>14.67824969925176</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.1348832436961856</v>
+        <v>0.6257483702159741</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.8920918483807494</v>
+        <v>-0.0556023631109943</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3071</v>
+        <v>2504</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>協禧</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>293.7801457374135</v>
+        <v>310.6127975392235</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.15</v>
+        <v>30.95</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>40.77081048642678</v>
+        <v>43.16377460421602</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>27.98064911385069</v>
+        <v>25.09243858182507</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.070085451502694</v>
+        <v>0.4802914770499117</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.2779771571013345</v>
+        <v>0.0326716940120571</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3023</v>
+        <v>2646</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>星宇航空</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>289.1406947468802</v>
+        <v>310.5995051111065</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>314.5</v>
+        <v>20.75</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.42272954599446</v>
+        <v>41.50283780106359</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.95519391835714</v>
+        <v>17.59629451187876</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9440030555553086</v>
+        <v>1.965926892903093</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>3.329549086439812</v>
+        <v>-0.0822300589362174</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>2477</v>
+        <v>3066</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>美隆電</t>
+          <t>李洲</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>275.5129159447002</v>
+        <v>305.340194608515</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>22.05</v>
+        <v>22.55</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>56.05359727179755</v>
+        <v>50.29544575487587</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.43031067455277</v>
+        <v>19.3891757059414</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.23914981233585</v>
+        <v>3.447992840226985</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1030945958912556</v>
+        <v>0.1527763254325799</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3095</v>
+        <v>3073</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>及成</t>
+          <t>天方能源</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>274.4808163954078</v>
+        <v>305.0462918429703</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>38.5</v>
+        <v>22.1</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.65722329488921</v>
+        <v>53.73079482690229</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.597417478273</v>
+        <v>20.68169556160542</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3421627512353389</v>
+        <v>0.4078559020457727</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.6012794504671088</v>
+        <v>0.0520028234179424</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>3018</v>
+        <v>3085</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>新零售</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>272.6298964985252</v>
+        <v>304.5047696586732</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>14</v>
+        <v>11.75</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>53.60532785290381</v>
+        <v>53.44326793618968</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.69427470890631</v>
+        <v>13.05060828317397</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6629896498525181</v>
+        <v>1.45034532031436</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0953194823264476</v>
+        <v>0.951588987715273</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>3050</v>
+        <v>2496</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>鈺德</t>
+          <t>卓越</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>270.155296175382</v>
+        <v>303.9891389872214</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>11.35</v>
+        <v>59.4</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.00024974920184</v>
+        <v>39.27390875432424</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>33.70127252941177</v>
+        <v>38.99775260467082</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9277149320029192</v>
+        <v>0.8911398655471982</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0359910622859193</v>
+        <v>0.1567590934338771</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>2538</v>
+        <v>2501</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>基泰</t>
+          <t>國建</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>265.6833873756258</v>
+        <v>303.4380578348697</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>9.17</v>
+        <v>22.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>27.75984988278913</v>
+        <v>43.77794615163543</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>23.2305972441462</v>
+        <v>25.04474904649135</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7798032001479241</v>
+        <v>0.6415007638695015</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0755008203781343</v>
+        <v>0.0310344934648875</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>3025</v>
+        <v>3060</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>星通</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>263.310167363024</v>
+        <v>299.2994207396545</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>54.8</v>
+        <v>29.55</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.12063165713359</v>
+        <v>47.40820166474667</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>38.56729088297195</v>
+        <v>23.02496503499644</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.591501483230651</v>
+        <v>0.9737597969185304</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.4944516290982617</v>
+        <v>0.2620894114027035</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>華固</t>
+          <t>皇昌</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>263.2200810270817</v>
+        <v>297.7816852075697</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>93.8</v>
+        <v>38.9</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>30.71034022421003</v>
+        <v>50.14558381475259</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25.09058403273412</v>
+        <v>12.39351662212618</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8289131000967072</v>
+        <v>0.7857299181036159</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.253794605798685</v>
+        <v>0.308277961194473</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>3024</v>
+        <v>3093</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>憶聲</t>
+          <t>港建*</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>263.1342669299617</v>
+        <v>297.717852375314</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>13.1</v>
+        <v>48</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>55.01807316863186</v>
+        <v>44.7160175716494</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.0213869819946</v>
+        <v>32.43471002480614</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3169031697045176</v>
+        <v>0.2994109505423246</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0204344271593557</v>
+        <v>0.8072366987866797</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>3045</v>
+        <v>2601</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>259.0723740504961</v>
+        <v>297.5212102614102</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>110.5</v>
+        <v>6.32</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.00366157152737</v>
+        <v>49.2704801971728</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.89244490289979</v>
+        <v>15.83757078601122</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7273873422068878</v>
+        <v>0.4196565368759983</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0799351700117605</v>
+        <v>-0.0553170553549568</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>3067</v>
+        <v>2489</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>全域</t>
+          <t>瑞軒</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>249.6570669445984</v>
+        <v>296.6200899080137</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>18</v>
+        <v>33.4</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>53.08787472537996</v>
+        <v>50.30184868441617</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8.833192734132446</v>
+        <v>35.58132726560577</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4532886088572594</v>
+        <v>1.302878452483696</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.95163543301905</v>
+        <v>0.9257096644621096</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>3013</v>
+        <v>2949</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>欣新網</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>245.5313467673019</v>
+        <v>296.0386053580718</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>87.2</v>
+        <v>62.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.38319597649321</v>
+        <v>51.57058808969348</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>40.63965315535031</v>
+        <v>14.89546132722419</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.665197839012465</v>
+        <v>0.1348832436961856</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>1.422334790556644</v>
+        <v>0.8920918483807494</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>2530</v>
+        <v>3071</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>華建</t>
+          <t>協禧</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>233.047986598629</v>
+        <v>293.7801457374135</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>19.4</v>
+        <v>26.15</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.95381424952147</v>
+        <v>40.77081048642678</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.19607531185875</v>
+        <v>27.98064911385069</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6252186508471638</v>
+        <v>1.070085451502694</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0742162840895865</v>
+        <v>0.2779771571013345</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>2468</v>
+        <v>3023</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>華經</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>230.5011050944921</v>
+        <v>289.1406947468802</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>34.95</v>
+        <v>314.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.60223578524301</v>
+        <v>53.42272954599446</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.32330897239376</v>
+        <v>15.95519391835714</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6950163377194679</v>
+        <v>0.9440030555553086</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1910824039899571</v>
+        <v>3.329549086439812</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3030</v>
+        <v>2706</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>第一店</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>229.9203515379244</v>
+        <v>286.3204519267896</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>296.5</v>
+        <v>12.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>49.86696368844171</v>
+        <v>45.51120392007492</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.00587670367006</v>
+        <v>20.37192280490914</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6138547899998582</v>
+        <v>0.437448786866192</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>3.969347862388947</v>
+        <v>-0.0413979417627861</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>2506</v>
+        <v>2477</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>太設</t>
+          <t>美隆電</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>225.1940278609767</v>
+        <v>275.5129159447002</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>8.630000000000001</v>
+        <v>22.05</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45.08233870668965</v>
+        <v>56.05359727179755</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>28.97639760658324</v>
+        <v>12.43031067455277</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2407948365357218</v>
+        <v>1.23914981233585</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0053802893716044</v>
+        <v>0.1030945958912556</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>2471</v>
+        <v>3095</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>資通</t>
+          <t>及成</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>220.1983833703981</v>
+        <v>274.4808163954078</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>49.5</v>
+        <v>38.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.89798242207911</v>
+        <v>51.65722329488921</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>33.01398089836219</v>
+        <v>11.597417478273</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.014352447426555</v>
+        <v>0.3421627512353389</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1240789966091058</v>
+        <v>0.6012794504671088</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3043</v>
+        <v>3018</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>科風</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>215.3562292995428</v>
+        <v>272.6298964985252</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>20.6</v>
+        <v>14</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.23907279045809</v>
+        <v>53.60532785290381</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>23.81323065793821</v>
+        <v>14.69427470890631</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8195527881243282</v>
+        <v>0.6629896498525181</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0823036149552723</v>
+        <v>-0.0953194823264476</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>3021</v>
+        <v>3050</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>鴻名</t>
+          <t>鈺德</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>215.1196312508627</v>
+        <v>270.155296175382</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>21</v>
+        <v>11.35</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>41.15202118422799</v>
+        <v>44.00024974920184</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.48343651763358</v>
+        <v>33.70127252941177</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2930869008249046</v>
+        <v>0.9277149320029192</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1683778287083641</v>
+        <v>0.0359910622859193</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>2453</v>
+        <v>2702</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>華園</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>214.7713514768863</v>
+        <v>268.004634446082</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>52.6</v>
+        <v>12.45</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.63020366720222</v>
+        <v>40.20150321977477</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>24.82160895556145</v>
+        <v>19.6234748230181</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.6599673656856228</v>
+        <v>0.6389256653500085</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.3070959879066399</v>
+        <v>-0.0281929688452965</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>3058</v>
+        <v>2538</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>立德</t>
+          <t>基泰</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>214.3529100386987</v>
+        <v>265.6833873756258</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>8.19</v>
+        <v>9.17</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>37.88854657965452</v>
+        <v>27.75984988278913</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>19.03850771260217</v>
+        <v>23.2305972441462</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7579379484056327</v>
+        <v>0.7798032001479241</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0072088019608583</v>
+        <v>-0.0755008203781343</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3015</v>
+        <v>3025</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>全漢</t>
+          <t>星通</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>214.134597703178</v>
+        <v>263.310167363024</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>58.7</v>
+        <v>54.8</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>53.44245551345467</v>
+        <v>42.12063165713359</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.52293889323226</v>
+        <v>38.56729088297195</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.357656443376901</v>
+        <v>0.591501483230651</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.4910984448955564</v>
+        <v>0.4944516290982617</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>3092</v>
+        <v>2548</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>鴻碩</t>
+          <t>華固</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>210.182548598484</v>
+        <v>263.2200810270817</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>23.6</v>
+        <v>93.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.89095788184204</v>
+        <v>30.71034022421003</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>25.77197500876651</v>
+        <v>25.09058403273412</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5935378305341218</v>
+        <v>0.8289131000967072</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.2195815136423975</v>
+        <v>-0.253794605798685</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>2537</v>
+        <v>3024</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>聯上發</t>
+          <t>憶聲</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>206.0467724786288</v>
+        <v>263.1342669299617</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>11</v>
+        <v>13.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.68868943929539</v>
+        <v>55.01807316863186</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.3556326761409</v>
+        <v>18.0213869819946</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.922287096784193</v>
+        <v>0.3169031697045176</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0138386975087201</v>
+        <v>0.0204344271593557</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>3019</v>
+        <v>3045</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>196.89520699479</v>
+        <v>259.0723740504961</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>134.5</v>
+        <v>110.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.98155061827713</v>
+        <v>40.00366157152737</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.23324675487554</v>
+        <v>15.89244490289979</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7299602715985796</v>
+        <v>0.7273873422068878</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.8329877608254419</v>
+        <v>-0.0799351700117605</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>2482</v>
+        <v>2705</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>連宇</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>192.5328172978725</v>
+        <v>250.181236062358</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>16.15</v>
+        <v>16.2</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>39.60129915350226</v>
+        <v>51.13057492466938</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>17.20398625964065</v>
+        <v>26.78162325361</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.277621292174088</v>
+        <v>0.0675546392216272</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1599312266957366</v>
+        <v>-0.0137305609739889</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>3011</v>
+        <v>3067</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>今皓</t>
+          <t>全域</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>192.4197249435952</v>
+        <v>249.6570669445984</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>11.45</v>
+        <v>18</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>36.23681214397042</v>
+        <v>53.08787472537996</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>32.75539987122387</v>
+        <v>8.833192734132446</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.05587826352936</v>
+        <v>0.4532886088572594</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0366088452678798</v>
+        <v>0.95163543301905</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>2460</v>
+        <v>3013</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>建通</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>192.3009282156884</v>
+        <v>245.5313467673019</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>31.8</v>
+        <v>87.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>49.58538373756911</v>
+        <v>46.38319597649321</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.9570055541829</v>
+        <v>40.63965315535031</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.9656093341897396</v>
+        <v>0.665197839012465</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1828967426156453</v>
+        <v>1.422334790556644</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>2457</v>
+        <v>2530</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>飛宏</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>188.1979446027292</v>
+        <v>233.047986598629</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>23.55</v>
+        <v>19.4</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.37587801132271</v>
+        <v>46.95381424952147</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>28.64778814008756</v>
+        <v>19.19607531185875</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4884879906647766</v>
+        <v>0.6252186508471638</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.1981785676573273</v>
+        <v>-0.0742162840895865</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>2640</v>
+        <v>2468</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>華經</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>185.4043108964773</v>
+        <v>230.5011050944921</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>147</v>
+        <v>34.95</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45.49607090917456</v>
+        <v>49.60223578524301</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>18.2604768929204</v>
+        <v>13.32330897239376</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.769502388942193</v>
+        <v>0.6950163377194679</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.2297304079979696</v>
+        <v>0.1910824039899571</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3038</v>
+        <v>3030</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>全台</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>182.5585825649678</v>
+        <v>229.9203515379244</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>20.7</v>
+        <v>296.5</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>43.60661892575844</v>
+        <v>49.86696368844171</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>30.77753347846167</v>
+        <v>17.00587670367006</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5145587850676108</v>
+        <v>0.6138547899998582</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.1128174976237982</v>
+        <v>3.969347862388947</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>2450</v>
+        <v>2506</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>神腦</t>
+          <t>太設</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>182.1611433555132</v>
+        <v>225.1940278609767</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>28.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>37.52638367659294</v>
+        <v>45.08233870668965</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>9.852979464487486</v>
+        <v>28.97639760658324</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.731239250744365</v>
+        <v>0.2407948365357218</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0128769114735406</v>
+        <v>-0.0053802893716044</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>3122</v>
+        <v>2617</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>笙泉</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>181.5064153956764</v>
+        <v>223.1640217663598</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>25.3</v>
+        <v>29.3</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>42.27845556013621</v>
+        <v>53.05719625408867</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>22.24004334222683</v>
+        <v>19.20623877906708</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.3404455345779316</v>
+        <v>1.115497818610819</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.2634204581504564</v>
+        <v>0.0779485693975745</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>2514</v>
+        <v>2471</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>龍邦</t>
+          <t>資通</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>181.0964613913409</v>
+        <v>220.1983833703981</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>12.25</v>
+        <v>49.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>30.83432362540981</v>
+        <v>46.89798242207911</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>21.4418807685983</v>
+        <v>33.01398089836219</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.5926427758510991</v>
+        <v>1.014352447426555</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0414684009642795</v>
+        <v>0.1240789966091058</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>3062</v>
+        <v>2636</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>台驊控股</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>174.101419738615</v>
+        <v>218.6920835702236</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>20.9</v>
+        <v>65.8</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>44.15696051603119</v>
+        <v>46.52680921578585</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>42.72242914661836</v>
+        <v>24.63260301864669</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.5244479865912921</v>
+        <v>0.5993415827806927</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.2531443268047686</v>
+        <v>0.117194795037083</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7470,21 +7470,21 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>2524</v>
+        <v>3043</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>科風</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>170.9830949795513</v>
+        <v>215.3562292995428</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>34.25</v>
+        <v>20.6</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,13 +7495,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>41.41760621373264</v>
+        <v>49.23907279045809</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>17.76689532035129</v>
+        <v>23.81323065793821</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.3048468502564098</v>
+        <v>0.8195527881243282</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.2162434011443171</v>
+        <v>0.0823036149552723</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3041</v>
+        <v>3021</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>揚智</t>
+          <t>鴻名</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>170.9712025460782</v>
+        <v>215.1196312508627</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>24.55</v>
+        <v>21</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>53.64740445760543</v>
+        <v>41.15202118422799</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>22.16417610273757</v>
+        <v>17.48343651763358</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.123393777672592</v>
+        <v>0.2930869008249046</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.2410351877645156</v>
+        <v>0.1683778287083641</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3049</v>
+        <v>2453</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>精金</t>
+          <t>凌群</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>163.1301146709576</v>
+        <v>214.7713514768863</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>11</v>
+        <v>52.6</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>46.90769954790059</v>
+        <v>46.63020366720222</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>32.80456063989357</v>
+        <v>24.82160895556145</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.8559791625282792</v>
+        <v>0.6599673656856228</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.1416629088455604</v>
+        <v>0.3070959879066399</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>2444</v>
+        <v>3058</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>兆勁</t>
+          <t>立德</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>163.0729108938985</v>
+        <v>214.3529100386987</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>11.4</v>
+        <v>8.19</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>48.7682040416599</v>
+        <v>37.88854657965452</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>33.53447117205059</v>
+        <v>19.03850771260217</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.258458217173057</v>
+        <v>0.7579379484056327</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.0730882532261992</v>
+        <v>-0.0072088019608583</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>2534</v>
+        <v>3015</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>宏盛</t>
+          <t>全漢</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>157.270537242208</v>
+        <v>214.134597703178</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>17.15</v>
+        <v>58.7</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>50.11919403105799</v>
+        <v>53.44245551345467</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>11.40179052061598</v>
+        <v>13.52293889323226</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.4733762394667629</v>
+        <v>1.357656443376901</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.0171612087536242</v>
+        <v>0.4910984448955564</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3057</v>
+        <v>2616</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>喬鼎</t>
+          <t>山隆</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>156.1321363857842</v>
+        <v>213.056682666536</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>15.7</v>
+        <v>13.4</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>45.84407813464412</v>
+        <v>44.74844342331964</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>31.68862815337083</v>
+        <v>10.41187995101043</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.333856891972247</v>
+        <v>0.5420182252608651</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.2240996368609424</v>
+        <v>-0.0271717924567286</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3047</v>
+        <v>3092</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>訊舟</t>
+          <t>鴻碩</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>144.759347360387</v>
+        <v>210.182548598484</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>14.6</v>
+        <v>23.6</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>47.36550718807118</v>
+        <v>39.89095788184204</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>21.41827704085187</v>
+        <v>25.77197500876651</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.5923900917200817</v>
+        <v>0.5935378305341218</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.0399761211672139</v>
+        <v>0.2195815136423975</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>2505</v>
+        <v>2537</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>139.4127120449387</v>
+        <v>206.0467724786288</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>18.1</v>
+        <v>11</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>54.66921244908163</v>
+        <v>50.68868943929539</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>10.36127060431423</v>
+        <v>12.3556326761409</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.5826182217585297</v>
+        <v>0.922287096784193</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.03925756268219</v>
+        <v>-0.0138386975087201</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>2515</v>
+        <v>3019</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>138.1054137365212</v>
+        <v>196.89520699479</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>11.95</v>
+        <v>134.5</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>40.31275190752972</v>
+        <v>48.98155061827713</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>13.54268307504715</v>
+        <v>15.23324675487554</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.02555667350364</v>
+        <v>0.7299602715985796</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.0151944367111718</v>
+        <v>0.8329877608254419</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7947,21 +7947,21 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>2608</v>
+        <v>2482</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>連宇</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>114.2986054046838</v>
+        <v>192.5328172978725</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>28.6</v>
+        <v>16.15</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>36.69746396231317</v>
+        <v>39.60129915350226</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12.76340238871474</v>
+        <v>17.20398625964065</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.7544243637896575</v>
+        <v>0.277621292174088</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,62 +7990,1281 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.082901007120757</v>
+        <v>-0.1599312266957366</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
+        <v>3011</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>今皓</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>192.4197249435952</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>36.23681214397042</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>32.75539987122387</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>1.05587826352936</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>0.0366088452678798</v>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>2460</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>建通</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>192.3009282156884</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>49.58538373756911</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>18.9570055541829</v>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.9656093341897396</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>0.1828967426156453</v>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>2457</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>飛宏</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>188.1979446027292</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>45.37587801132271</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>28.64778814008756</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>0.4884879906647766</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>0.1981785676573273</v>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>2640</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>185.4043108964773</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>45.49607090917456</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>18.2604768929204</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>0.769502388942193</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>0.2297304079979696</v>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>2701</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>萬企</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>185.0499944506264</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>44.63090998234926</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>23.688315234555</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.60528262168236</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>-0.0295521768694975</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>2722</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>夏都</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>184.1973549961578</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>48.03372305160061</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>16.00546052719994</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0.3101940442121724</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>0.0635691083864878</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>3038</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>182.5585825649678</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>43.60661892575844</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>30.77753347846167</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>0.5145587850676108</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>0.1128174976237982</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>2450</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>神腦</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>182.1611433555132</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>37.52638367659294</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>9.852979464487486</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.731239250744365</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>-0.0128769114735406</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>3122</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>笙泉</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>181.5064153956764</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>42.27845556013621</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>22.24004334222683</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>0.3404455345779316</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>0.2634204581504564</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>2514</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>龍邦</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>181.0964613913409</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30.83432362540981</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>21.4418807685983</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.5926427758510991</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>-0.0414684009642795</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>3062</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>建漢</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>174.101419738615</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>44.15696051603119</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>42.72242914661836</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.5244479865912921</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>0.2531443268047686</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>2524</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>京城</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>170.9830949795513</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>41.41760621373264</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>17.76689532035129</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.3048468502564098</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>-0.2162434011443171</v>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>3041</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>揚智</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>170.9712025460782</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>53.64740445760543</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>22.16417610273757</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>1.123393777672592</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>0.2410351877645156</v>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>3049</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>精金</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>163.1301146709576</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>46.90769954790059</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>32.80456063989357</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.8559791625282792</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>0.1416629088455604</v>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>2444</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>兆勁</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>163.0729108938985</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>48.7682040416599</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>33.53447117205059</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>1.258458217173057</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>0.0730882532261992</v>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>2534</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>宏盛</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>157.270537242208</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>50.11919403105799</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>11.40179052061598</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>0.4733762394667629</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>0.0171612087536242</v>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>3057</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>喬鼎</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>156.1321363857842</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>45.84407813464412</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>31.68862815337083</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.333856891972247</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>0.2240996368609424</v>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>3047</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>訊舟</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>144.759347360387</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>47.36550718807118</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>21.41827704085187</v>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0.5923900917200817</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>0.0399761211672139</v>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2505</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>國揚</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>139.4127120449387</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>54.66921244908163</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>10.36127060431423</v>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>0.5826182217585297</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N161" s="2" t="n">
+        <v>0.03925756268219</v>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>2515</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>中工</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>138.1054137365212</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>40.31275190752972</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>13.54268307504715</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>1.02555667350364</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>0.0151944367111718</v>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>2614</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>東森</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>117.1128830769138</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>49.37139300711747</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>16.35198443318947</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>0.5195587564865379</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>0.0160169385543482</v>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>2608</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>嘉里大榮</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>114.2986054046838</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>36.69746396231317</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>12.76340238871474</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>0.7544243637896575</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>-0.082901007120757</v>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>2642</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>宅配通</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>82.53001733093927</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>46.28349232178952</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>14.10348743127417</v>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>0.4131188357153665</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>0.0233170901314448</v>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
         <v>3027</v>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>盛達</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D143" s="2" t="n">
+      <c r="C166" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D166" s="2" t="n">
         <v>58.95690232688368</v>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E166" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H143" s="2" t="n">
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H166" s="2" t="n">
         <v>45.38315222088539</v>
       </c>
-      <c r="I143" s="2" t="n">
+      <c r="I166" s="2" t="n">
         <v>18.40807185387341</v>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J166" s="2" t="n">
         <v>0.537821821455579</v>
       </c>
-      <c r="K143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N143" s="2" t="n">
+      <c r="K166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N166" s="2" t="n">
         <v>0.0478965109216358</v>
       </c>
-      <c r="O143" s="2" t="inlineStr">
+      <c r="O166" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
